--- a/seo-texts/guest-posts/donors-prioritized.xlsx
+++ b/seo-texts/guest-posts/donors-prioritized.xlsx
@@ -1140,7 +1140,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>moiton.ru</t>
+          <t>krasnodar.bz</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1149,22 +1149,22 @@
         </is>
       </c>
       <c r="D10" s="3" t="n">
-        <v>700</v>
+        <v>2499</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>100</v>
+        <v>499</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>800</v>
+        <v>2998</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H10" s="4" t="n">
-        <v>65.70999999999999</v>
+        <v>23.21</v>
       </c>
       <c r="I10" s="4" t="n">
-        <v>48.4</v>
+        <v>48</v>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
@@ -1173,42 +1173,36 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>30-40%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>4.828800201416016</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>12180</t>
-        </is>
+          <t>40-50%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>36</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>342</v>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>meyer-corp.ru</t>
+          <t>Meyer</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Лучше размещать под meyer-corp.ru, потому что можно мягко зайти через тему автоматизации производства, сортировки сырья и снижения ручного труда.</t>
+          <t>Послеуборочная обработка урожая на Кубани, фотосепарация зерна и семян</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>«Как автоматизация сортировки помогает производству снижать брак и экономить сырьё»</t>
+          <t>«Как фотосепараторы помогают аграриям Кубани повысить качество зерна и семян»</t>
         </is>
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>нет dofollow в выборке</t>
+          <t>проверить индексацию site: вручную</t>
         </is>
       </c>
     </row>
@@ -1218,7 +1212,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>krasnodar.bz</t>
+          <t>arh112.ru</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1227,22 +1221,22 @@
         </is>
       </c>
       <c r="D11" s="3" t="n">
-        <v>2499</v>
+        <v>500</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>2998</v>
+        <v>1000</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>58</v>
+        <v>42</v>
       </c>
       <c r="H11" s="4" t="n">
-        <v>23.21</v>
+        <v>84</v>
       </c>
       <c r="I11" s="4" t="n">
-        <v>48</v>
+        <v>47.8</v>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
@@ -1251,17 +1245,23 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>40-50%</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>36</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>342</v>
+          <t>50-60%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>4.916699886322021</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>Послеуборочная обработка урожая на Кубани, фотосепарация зерна и семян</t>
+          <t>Инвестиции в сортировочное оборудование / окупаемость переработки сырья</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
-          <t>«Как фотосепараторы помогают аграриям Кубани повысить качество зерна и семян»</t>
+          <t>«Инвестиции в сортировочное оборудование: как фотосепараторы повышают доходность переработки сырья»</t>
         </is>
       </c>
       <c r="R11" s="2" t="inlineStr">
@@ -1290,7 +1290,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>arh112.ru</t>
+          <t>bouw.ru</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1299,26 +1299,26 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>500</v>
+        <v>2600</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>500</v>
+        <v>410</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1000</v>
+        <v>3010</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>84</v>
+        <v>25.77</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>47.8</v>
+        <v>55.49</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>РУЧНАЯ ПРОВЕРКА</t>
+          <t>НЕ БРАТЬ (фильтр)</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1326,39 +1326,33 @@
           <t>50-60%</t>
         </is>
       </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>4.916699886322021</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>171</t>
-        </is>
+      <c r="L12" s="2" t="n">
+        <v>4.785699844360352</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>1868</v>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>ProKompressor</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Инвестиции в сортировочное оборудование / окупаемость переработки сырья</t>
+          <t>Практический материал для строителей/ремонтных бригад, подбор компрессора</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>«Инвестиции в сортировочное оборудование: как фотосепараторы повышают доходность переработки сырья»</t>
+          <t>«Как выбрать компрессор для строительных и ремонтных работ: покраска, продувка, пневмоинструмент и пескоструй»</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>проверить индексацию site: вручную</t>
+          <t>токсичен: редакционные размещения под займы/МФО</t>
         </is>
       </c>
     </row>
@@ -1368,7 +1362,7 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>bouw.ru</t>
+          <t>domocvet.com</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1377,22 +1371,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>2600</v>
+        <v>504</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>410</v>
+        <v>240</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>3010</v>
+        <v>744</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>67</v>
+        <v>45</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>25.77</v>
+        <v>89.29000000000001</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>55.49</v>
+        <v>48.75</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -1401,17 +1395,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>50-60%</t>
+          <t>40-50%</t>
         </is>
       </c>
       <c r="L13" s="2" t="n">
-        <v>4.785699844360352</v>
+        <v>4.913000106811523</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>1868</v>
+        <v>6612</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -1420,12 +1414,12 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Практический материал для строителей/ремонтных бригад, подбор компрессора</t>
+          <t>Производственная энергоэффективность, подбор винтового компрессора</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>«Как выбрать компрессор для строительных и ремонтных работ: покраска, продувка, пневмоинструмент и пескоструй»</t>
+          <t>«Сжатый воздух на производстве: как правильно подобрать винтовой компрессор и снизить расходы на энергию»</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
@@ -1440,7 +1434,7 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>domocvet.com</t>
+          <t>moiton.ru</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1449,22 +1443,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>504</v>
+        <v>700</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>240</v>
+        <v>100</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>744</v>
+        <v>800</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>89.29000000000001</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>48.75</v>
+        <v>48.4</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1473,36 +1467,42 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40-50%</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>4.913000106811523</v>
-      </c>
-      <c r="M14" s="2" t="n">
-        <v>28</v>
-      </c>
-      <c r="N14" s="2" t="n">
-        <v>6612</v>
+          <t>30-40%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4.828800201416016</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>12180</t>
+        </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ProKompressor</t>
+          <t>meyer-corp.ru</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>Производственная энергоэффективность, подбор винтового компрессора</t>
+          <t>Лучше размещать под meyer-corp.ru, потому что можно мягко зайти через тему автоматизации производства, сортировки сырья и снижения ручного труда.</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>«Сжатый воздух на производстве: как правильно подобрать винтовой компрессор и снизить расходы на энергию»</t>
+          <t>«Как автоматизация сортировки помогает производству снижать брак и экономить сырьё»</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>токсичен: редакционные размещения под займы/МФО</t>
+          <t>токсичен: аренда dofollow на год: аудит 50 статей - ссылки вычищаются (44/50 без внешних, dofollow только 2020-21), тематика нерелевантна</t>
         </is>
       </c>
     </row>
@@ -2395,7 +2395,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>moiton.ru</t>
+          <t>moscow-baku.ru</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -2404,22 +2404,22 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>700</v>
+        <v>799</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>100</v>
+        <v>399</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>800</v>
+        <v>1198</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="H12" s="4" t="n">
-        <v>70</v>
+        <v>58.82</v>
       </c>
       <c r="I12" s="4" t="n">
-        <v>50.35</v>
+        <v>48.76</v>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
@@ -2433,37 +2433,37 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4.828800201416016</t>
+          <t>4.826099872589111</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>48</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12180</t>
+          <t>871</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>meyer-corp.ru</t>
+          <t>ProKompressor</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>Лучше размещать под meyer-corp.ru, потому что можно мягко зайти через тему автоматизации производства, сортировки сырья и снижения ручного труда.</t>
+          <t>Промышленное сотрудничество России и Азербайджана, модернизация предприятий</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
         <is>
-          <t>«Как автоматизация сортировки помогает производству снижать брак и экономить сырьё»</t>
+          <t>«Компрессорное оборудование для промышленных проектов России и Азербайджана: как предприятия выбирают надёжные решения»</t>
         </is>
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>нет dofollow в выборке</t>
+          <t>проверить индексацию site: вручную</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>moscow-baku.ru</t>
+          <t>ftimes.ru</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2482,22 +2482,22 @@
         </is>
       </c>
       <c r="D13" s="3" t="n">
-        <v>799</v>
+        <v>3596</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>399</v>
+        <v>450</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1198</v>
+        <v>4046</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="H13" s="4" t="n">
-        <v>58.82</v>
+        <v>15.85</v>
       </c>
       <c r="I13" s="4" t="n">
-        <v>48.76</v>
+        <v>45.51</v>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
@@ -2506,23 +2506,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>30-40%</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>4.826099872589111</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>871</t>
-        </is>
+          <t>40-50%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>4.948100090026855</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>42</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>80</v>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
@@ -2531,17 +2525,17 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>Промышленное сотрудничество России и Азербайджана, модернизация предприятий</t>
+          <t>тема не «купить компрессор», а производственная экономика: как предприятия снижают простои, энергозатраты и риски за счёт правильного подбора компрессорной системы.</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
-          <t>«Компрессорное оборудование для промышленных проектов России и Азербайджана: как предприятия выбирают надёжные решения»</t>
+          <t>«Сжатый воздух как скрытая статья расходов: как предприятия выбирают компрессорное оборудование в 2026 году»</t>
         </is>
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>проверить индексацию site: вручную</t>
+          <t>токсичность снята; трафик 80 - мёртвая?</t>
         </is>
       </c>
     </row>
@@ -2551,7 +2545,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>ftimes.ru</t>
+          <t>bobr.by</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2560,22 +2554,22 @@
         </is>
       </c>
       <c r="D14" s="3" t="n">
-        <v>3596</v>
+        <v>3000</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>450</v>
+        <v>1700</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>4046</v>
+        <v>4700</v>
       </c>
       <c r="G14" s="4" t="n">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="H14" s="4" t="n">
-        <v>15.85</v>
+        <v>18.33</v>
       </c>
       <c r="I14" s="4" t="n">
-        <v>45.51</v>
+        <v>44.83</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -2588,32 +2582,32 @@
         </is>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.948100090026855</v>
+        <v>4.759500026702881</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>80</v>
+        <v>27613</v>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>ProKompressor</t>
+          <t>Meyer</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>тема не «купить компрессор», а производственная экономика: как предприятия снижают простои, энергозатраты и риски за счёт правильного подбора компрессорной системы.</t>
+          <t>Агро/пищевое производство, сортировка сырья, снижение потерь</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>«Сжатый воздух как скрытая статья расходов: как предприятия выбирают компрессорное оборудование в 2026 году»</t>
+          <t>«Как фотосепараторы помогают агропредприятиям повысить качество зерна и снизить потери сырья»</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>токсичность снята; трафик 80 - мёртвая?</t>
+          <t>нет dofollow в выборке</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2617,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>bobr.by</t>
+          <t>zheltaya.ru</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2632,22 +2626,22 @@
         </is>
       </c>
       <c r="D15" s="3" t="n">
-        <v>3000</v>
+        <v>183</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>1700</v>
+        <v>122</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>4700</v>
+        <v>305</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>55</v>
+        <v>34</v>
       </c>
       <c r="H15" s="4" t="n">
-        <v>18.33</v>
+        <v>185.79</v>
       </c>
       <c r="I15" s="4" t="n">
-        <v>44.83</v>
+        <v>40.6</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -2656,36 +2650,36 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>40-50%</t>
+          <t>30-40%</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4.759500026702881</v>
+        <v>5</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>27613</v>
+        <v>68</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>Meyer</t>
+          <t>Meyer, но слабо</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>Агро/пищевое производство, сортировка сырья, снижение потерь</t>
+          <t>Оптическая сортировка, качество продукции на производстве</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
         <is>
-          <t>«Как фотосепараторы помогают агропредприятиям повысить качество зерна и снизить потери сырья»</t>
+          <t>«От зерна до готового продукта: как фотосепараторы повышают качество на производстве»</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>нет dofollow в выборке</t>
+          <t>проверить индексацию site: вручную</t>
         </is>
       </c>
     </row>
@@ -2695,7 +2689,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>zheltaya.ru</t>
+          <t>moiton.ru</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2704,26 +2698,26 @@
         </is>
       </c>
       <c r="D16" s="3" t="n">
-        <v>183</v>
+        <v>700</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>305</v>
+        <v>800</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="H16" s="4" t="n">
-        <v>185.79</v>
+        <v>70</v>
       </c>
       <c r="I16" s="4" t="n">
-        <v>40.6</v>
+        <v>50.35</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>РУЧНАЯ ПРОВЕРКА</t>
+          <t>НЕ БРАТЬ (фильтр)</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2731,33 +2725,39 @@
           <t>30-40%</t>
         </is>
       </c>
-      <c r="L16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="M16" s="2" t="n">
-        <v>17</v>
-      </c>
-      <c r="N16" s="2" t="n">
-        <v>68</v>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>4.828800201416016</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>12180</t>
+        </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Meyer, но слабо</t>
+          <t>meyer-corp.ru</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>Оптическая сортировка, качество продукции на производстве</t>
+          <t>Лучше размещать под meyer-corp.ru, потому что можно мягко зайти через тему автоматизации производства, сортировки сырья и снижения ручного труда.</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
         <is>
-          <t>«От зерна до готового продукта: как фотосепараторы повышают качество на производстве»</t>
+          <t>«Как автоматизация сортировки помогает производству снижать брак и экономить сырьё»</t>
         </is>
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>проверить индексацию site: вручную</t>
+          <t>токсичен: аренда dofollow на год: аудит 50 статей - ссылки вычищаются (44/50 без внешних, dofollow только 2020-21), тематика нерелевантна</t>
         </is>
       </c>
     </row>
